--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>['38']</t>
+  </si>
+  <si>
+    <t>['17', '44']</t>
   </si>
   <si>
     <t>['35']</t>
@@ -1164,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1626,7 +1629,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2244,7 +2247,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2656,7 +2659,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3274,7 +3277,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3355,7 +3358,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ11">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3480,7 +3483,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3892,7 +3895,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -3970,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ14">
         <v>2.22</v>
@@ -4304,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4716,7 +4719,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4922,7 +4925,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5128,7 +5131,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5334,7 +5337,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6982,7 +6985,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7188,7 +7191,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7394,7 +7397,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7887,7 +7890,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ33">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8090,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ34">
         <v>0.78</v>
@@ -8424,7 +8427,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8836,7 +8839,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9042,7 +9045,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9454,7 +9457,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9660,7 +9663,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9866,7 +9869,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10278,7 +10281,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10484,7 +10487,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10690,7 +10693,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10768,7 +10771,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ47">
         <v>2.38</v>
@@ -10896,7 +10899,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11308,7 +11311,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11389,7 +11392,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ50">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11720,7 +11723,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11926,7 +11929,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12338,7 +12341,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12544,7 +12547,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12750,7 +12753,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q57">
         <v>3.6</v>
@@ -12956,7 +12959,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13162,7 +13165,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -15634,7 +15637,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15840,7 +15843,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16252,7 +16255,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16458,7 +16461,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16664,7 +16667,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16870,7 +16873,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17488,7 +17491,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17694,7 +17697,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17775,7 +17778,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -17900,7 +17903,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18106,7 +18109,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18312,7 +18315,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18518,7 +18521,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18724,7 +18727,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19136,7 +19139,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19626,7 +19629,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19754,7 +19757,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19960,7 +19963,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20578,7 +20581,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21196,7 +21199,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21483,7 +21486,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ99">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21814,7 +21817,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22098,7 +22101,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22226,7 +22229,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22432,7 +22435,7 @@
         <v>154</v>
       </c>
       <c r="P104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22638,7 +22641,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22844,7 +22847,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23668,7 +23671,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23874,7 +23877,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24573,7 +24576,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ114">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -25110,7 +25113,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25316,7 +25319,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q118">
         <v>3.5</v>
@@ -25600,7 +25603,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ119">
         <v>0.78</v>
@@ -25728,7 +25731,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26140,7 +26143,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26346,7 +26349,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26552,7 +26555,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26964,7 +26967,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27170,7 +27173,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27248,7 +27251,7 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ127">
         <v>1.75</v>
@@ -27376,7 +27379,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27582,7 +27585,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27994,7 +27997,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28075,7 +28078,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ131">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28200,7 +28203,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28612,7 +28615,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29436,7 +29439,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29642,7 +29645,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30054,7 +30057,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30260,7 +30263,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30466,7 +30469,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30878,7 +30881,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31084,7 +31087,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31290,7 +31293,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31496,7 +31499,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31702,7 +31705,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32114,7 +32117,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32320,7 +32323,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32526,7 +32529,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32683,6 +32686,212 @@
       </c>
       <c r="BP153">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7574707</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45669.52083333334</v>
+      </c>
+      <c r="F154">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>82</v>
+      </c>
+      <c r="H154" t="s">
+        <v>73</v>
+      </c>
+      <c r="I154">
+        <v>2</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>2</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>2</v>
+      </c>
+      <c r="O154" t="s">
+        <v>188</v>
+      </c>
+      <c r="P154" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q154">
+        <v>7.25</v>
+      </c>
+      <c r="R154">
+        <v>2.5</v>
+      </c>
+      <c r="S154">
+        <v>1.72</v>
+      </c>
+      <c r="T154">
+        <v>1.3</v>
+      </c>
+      <c r="U154">
+        <v>3.2</v>
+      </c>
+      <c r="V154">
+        <v>2.35</v>
+      </c>
+      <c r="W154">
+        <v>1.51</v>
+      </c>
+      <c r="X154">
+        <v>5.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.12</v>
+      </c>
+      <c r="Z154">
+        <v>9.51</v>
+      </c>
+      <c r="AA154">
+        <v>5.6</v>
+      </c>
+      <c r="AB154">
+        <v>1.28</v>
+      </c>
+      <c r="AC154">
+        <v>1.03</v>
+      </c>
+      <c r="AD154">
+        <v>11</v>
+      </c>
+      <c r="AE154">
+        <v>1.2</v>
+      </c>
+      <c r="AF154">
+        <v>4.5</v>
+      </c>
+      <c r="AG154">
+        <v>1.62</v>
+      </c>
+      <c r="AH154">
+        <v>2.21</v>
+      </c>
+      <c r="AI154">
+        <v>2.1</v>
+      </c>
+      <c r="AJ154">
+        <v>1.65</v>
+      </c>
+      <c r="AK154">
+        <v>3.4</v>
+      </c>
+      <c r="AL154">
+        <v>1.15</v>
+      </c>
+      <c r="AM154">
+        <v>1.06</v>
+      </c>
+      <c r="AN154">
+        <v>1.43</v>
+      </c>
+      <c r="AO154">
+        <v>1.86</v>
+      </c>
+      <c r="AP154">
+        <v>1.63</v>
+      </c>
+      <c r="AQ154">
+        <v>1.63</v>
+      </c>
+      <c r="AR154">
+        <v>1.23</v>
+      </c>
+      <c r="AS154">
+        <v>1.27</v>
+      </c>
+      <c r="AT154">
+        <v>2.5</v>
+      </c>
+      <c r="AU154">
+        <v>5</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>2</v>
+      </c>
+      <c r="AX154">
+        <v>7</v>
+      </c>
+      <c r="AY154">
+        <v>8</v>
+      </c>
+      <c r="AZ154">
+        <v>13</v>
+      </c>
+      <c r="BA154">
+        <v>1</v>
+      </c>
+      <c r="BB154">
+        <v>10</v>
+      </c>
+      <c r="BC154">
+        <v>11</v>
+      </c>
+      <c r="BD154">
+        <v>5.67</v>
+      </c>
+      <c r="BE154">
+        <v>11</v>
+      </c>
+      <c r="BF154">
+        <v>1.19</v>
+      </c>
+      <c r="BG154">
+        <v>1.27</v>
+      </c>
+      <c r="BH154">
+        <v>3.5</v>
+      </c>
+      <c r="BI154">
+        <v>1.5</v>
+      </c>
+      <c r="BJ154">
+        <v>2.5</v>
+      </c>
+      <c r="BK154">
+        <v>1.82</v>
+      </c>
+      <c r="BL154">
+        <v>1.98</v>
+      </c>
+      <c r="BM154">
+        <v>2.3</v>
+      </c>
+      <c r="BN154">
+        <v>1.57</v>
+      </c>
+      <c r="BO154">
+        <v>3</v>
+      </c>
+      <c r="BP154">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -583,6 +583,15 @@
     <t>['17', '44']</t>
   </si>
   <si>
+    <t>['11', '36', '67', '80']</t>
+  </si>
+  <si>
+    <t>['36', '63']</t>
+  </si>
+  <si>
+    <t>['20', '40']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -806,6 +815,15 @@
   </si>
   <si>
     <t>['59']</t>
+  </si>
+  <si>
+    <t>['2', '30', '68']</t>
+  </si>
+  <si>
+    <t>['3', '23', '88']</t>
+  </si>
+  <si>
+    <t>['56', '72']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1629,7 +1647,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2247,7 +2265,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2659,7 +2677,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3277,7 +3295,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3355,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ11">
         <v>1.63</v>
@@ -3483,7 +3501,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3767,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ13">
         <v>0.78</v>
@@ -3895,7 +3913,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -3976,7 +3994,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ14">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4179,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15">
         <v>1.38</v>
@@ -4307,7 +4325,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4388,7 +4406,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ16">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4591,10 +4609,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4719,7 +4737,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4925,7 +4943,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5006,7 +5024,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ19">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5131,7 +5149,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5212,7 +5230,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ20">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR20">
         <v>1.56</v>
@@ -5337,7 +5355,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -6033,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ24">
         <v>0.25</v>
@@ -6985,7 +7003,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7191,7 +7209,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7269,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ30">
         <v>0.63</v>
@@ -7397,7 +7415,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7684,7 +7702,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ32">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>0.64</v>
@@ -8299,10 +8317,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ35">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR35">
         <v>1.11</v>
@@ -8427,7 +8445,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8505,10 +8523,10 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR36">
         <v>1.59</v>
@@ -8839,7 +8857,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -8920,7 +8938,7 @@
         <v>1</v>
       </c>
       <c r="AQ38">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR38">
         <v>0.93</v>
@@ -9045,7 +9063,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9457,7 +9475,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9663,7 +9681,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9741,7 +9759,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ42">
         <v>1.5</v>
@@ -9869,7 +9887,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10281,7 +10299,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10487,7 +10505,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10693,7 +10711,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10899,7 +10917,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -10977,10 +10995,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11183,7 +11201,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ49">
         <v>0.25</v>
@@ -11311,7 +11329,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11389,7 +11407,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ50">
         <v>1.63</v>
@@ -11598,7 +11616,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ51">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR51">
         <v>1.08</v>
@@ -11723,7 +11741,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11929,7 +11947,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12010,7 +12028,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ53">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1</v>
@@ -12341,7 +12359,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12547,7 +12565,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12628,7 +12646,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR56">
         <v>0.98</v>
@@ -12753,7 +12771,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>3.6</v>
@@ -12959,7 +12977,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13165,7 +13183,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -13243,7 +13261,7 @@
         <v>0.67</v>
       </c>
       <c r="AP59">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ59">
         <v>0.67</v>
@@ -13658,7 +13676,7 @@
         <v>3</v>
       </c>
       <c r="AQ61">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>2.38</v>
@@ -14067,7 +14085,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ63">
         <v>1</v>
@@ -14479,10 +14497,10 @@
         <v>1.33</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15512,7 +15530,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ70">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -15637,7 +15655,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15715,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15843,7 +15861,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16255,7 +16273,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16333,7 +16351,7 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ74">
         <v>0.67</v>
@@ -16461,7 +16479,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16542,7 +16560,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR75">
         <v>0.89</v>
@@ -16667,7 +16685,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16873,7 +16891,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -16954,7 +16972,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ77">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR77">
         <v>1.24</v>
@@ -17363,7 +17381,7 @@
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ79">
         <v>0.44</v>
@@ -17491,7 +17509,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17697,7 +17715,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17903,7 +17921,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18109,7 +18127,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18187,7 +18205,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ83">
         <v>1.38</v>
@@ -18315,7 +18333,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18521,7 +18539,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18727,7 +18745,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -18808,7 +18826,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ86">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR86">
         <v>1.12</v>
@@ -19011,7 +19029,7 @@
         <v>1.2</v>
       </c>
       <c r="AP87">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ87">
         <v>0.78</v>
@@ -19139,7 +19157,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19426,7 +19444,7 @@
         <v>3</v>
       </c>
       <c r="AQ89">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>2.03</v>
@@ -19757,7 +19775,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19963,7 +19981,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20456,7 +20474,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR94">
         <v>1.13</v>
@@ -20581,7 +20599,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -21071,7 +21089,7 @@
         <v>1.6</v>
       </c>
       <c r="AP97">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ97">
         <v>1.11</v>
@@ -21199,7 +21217,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21280,7 +21298,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR98">
         <v>1.75</v>
@@ -21483,7 +21501,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ99">
         <v>1.63</v>
@@ -21817,7 +21835,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -21895,7 +21913,7 @@
         <v>1</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ101">
         <v>0.78</v>
@@ -22229,7 +22247,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22435,7 +22453,7 @@
         <v>154</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22516,7 +22534,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR104">
         <v>1</v>
@@ -22641,7 +22659,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22847,7 +22865,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23131,7 +23149,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ107">
         <v>0.67</v>
@@ -23546,7 +23564,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ109">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR109">
         <v>1.17</v>
@@ -23671,7 +23689,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23752,7 +23770,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ110">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>1.54</v>
@@ -23877,7 +23895,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24161,7 +24179,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ112">
         <v>1.11</v>
@@ -24367,7 +24385,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ113">
         <v>0.44</v>
@@ -25113,7 +25131,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25194,7 +25212,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ117">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR117">
         <v>1.23</v>
@@ -25319,7 +25337,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q118">
         <v>3.5</v>
@@ -25731,7 +25749,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26143,7 +26161,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26349,7 +26367,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26555,7 +26573,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26636,7 +26654,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR124">
         <v>1.55</v>
@@ -26967,7 +26985,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27045,7 +27063,7 @@
         <v>1.14</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ126">
         <v>1.11</v>
@@ -27173,7 +27191,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27379,7 +27397,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27460,7 +27478,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ128">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR128">
         <v>1.24</v>
@@ -27585,7 +27603,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27997,7 +28015,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28203,7 +28221,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28281,7 +28299,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ132">
         <v>2.38</v>
@@ -28490,7 +28508,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ133">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR133">
         <v>1.29</v>
@@ -28615,7 +28633,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -28693,7 +28711,7 @@
         <v>0.29</v>
       </c>
       <c r="AP134">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ134">
         <v>0.33</v>
@@ -28899,10 +28917,10 @@
         <v>0.5</v>
       </c>
       <c r="AP135">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ135">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR135">
         <v>2.03</v>
@@ -29439,7 +29457,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29645,7 +29663,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30057,7 +30075,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30263,7 +30281,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30341,7 +30359,7 @@
         <v>0.38</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ142">
         <v>0.33</v>
@@ -30469,7 +30487,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30881,7 +30899,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31087,7 +31105,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31165,10 +31183,10 @@
         <v>2.38</v>
       </c>
       <c r="AP146">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ146">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR146">
         <v>1.3</v>
@@ -31293,7 +31311,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31499,7 +31517,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31577,7 +31595,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ148">
         <v>2.38</v>
@@ -31705,7 +31723,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31786,7 +31804,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ149">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR149">
         <v>1.35</v>
@@ -31989,7 +32007,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ150">
         <v>0.78</v>
@@ -32117,7 +32135,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32198,7 +32216,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ151">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR151">
         <v>1.25</v>
@@ -32323,7 +32341,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32404,7 +32422,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ152">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.17</v>
@@ -32529,7 +32547,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32892,6 +32910,830 @@
       </c>
       <c r="BP154">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7574720</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45674.71875</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>83</v>
+      </c>
+      <c r="H155" t="s">
+        <v>75</v>
+      </c>
+      <c r="I155">
+        <v>2</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>4</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>189</v>
+      </c>
+      <c r="P155" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q155">
+        <v>1.62</v>
+      </c>
+      <c r="R155">
+        <v>2.75</v>
+      </c>
+      <c r="S155">
+        <v>11</v>
+      </c>
+      <c r="T155">
+        <v>1.29</v>
+      </c>
+      <c r="U155">
+        <v>3.5</v>
+      </c>
+      <c r="V155">
+        <v>2.25</v>
+      </c>
+      <c r="W155">
+        <v>1.57</v>
+      </c>
+      <c r="X155">
+        <v>5.5</v>
+      </c>
+      <c r="Y155">
+        <v>1.14</v>
+      </c>
+      <c r="Z155">
+        <v>1.2</v>
+      </c>
+      <c r="AA155">
+        <v>6.6</v>
+      </c>
+      <c r="AB155">
+        <v>14</v>
+      </c>
+      <c r="AC155">
+        <v>1</v>
+      </c>
+      <c r="AD155">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE155">
+        <v>1.16</v>
+      </c>
+      <c r="AF155">
+        <v>4.15</v>
+      </c>
+      <c r="AG155">
+        <v>1.67</v>
+      </c>
+      <c r="AH155">
+        <v>2.05</v>
+      </c>
+      <c r="AI155">
+        <v>2.2</v>
+      </c>
+      <c r="AJ155">
+        <v>1.62</v>
+      </c>
+      <c r="AK155">
+        <v>1.03</v>
+      </c>
+      <c r="AL155">
+        <v>1.11</v>
+      </c>
+      <c r="AM155">
+        <v>4.4</v>
+      </c>
+      <c r="AN155">
+        <v>2.67</v>
+      </c>
+      <c r="AO155">
+        <v>1.25</v>
+      </c>
+      <c r="AP155">
+        <v>2.7</v>
+      </c>
+      <c r="AQ155">
+        <v>1.11</v>
+      </c>
+      <c r="AR155">
+        <v>2.01</v>
+      </c>
+      <c r="AS155">
+        <v>1.32</v>
+      </c>
+      <c r="AT155">
+        <v>3.33</v>
+      </c>
+      <c r="AU155">
+        <v>12</v>
+      </c>
+      <c r="AV155">
+        <v>0</v>
+      </c>
+      <c r="AW155">
+        <v>8</v>
+      </c>
+      <c r="AX155">
+        <v>2</v>
+      </c>
+      <c r="AY155">
+        <v>22</v>
+      </c>
+      <c r="AZ155">
+        <v>2</v>
+      </c>
+      <c r="BA155">
+        <v>7</v>
+      </c>
+      <c r="BB155">
+        <v>2</v>
+      </c>
+      <c r="BC155">
+        <v>9</v>
+      </c>
+      <c r="BD155">
+        <v>1.1</v>
+      </c>
+      <c r="BE155">
+        <v>11</v>
+      </c>
+      <c r="BF155">
+        <v>7</v>
+      </c>
+      <c r="BG155">
+        <v>1.23</v>
+      </c>
+      <c r="BH155">
+        <v>3.55</v>
+      </c>
+      <c r="BI155">
+        <v>1.41</v>
+      </c>
+      <c r="BJ155">
+        <v>2.6</v>
+      </c>
+      <c r="BK155">
+        <v>1.67</v>
+      </c>
+      <c r="BL155">
+        <v>2.02</v>
+      </c>
+      <c r="BM155">
+        <v>2.02</v>
+      </c>
+      <c r="BN155">
+        <v>1.66</v>
+      </c>
+      <c r="BO155">
+        <v>2.55</v>
+      </c>
+      <c r="BP155">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7574718</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45675.52083333334</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>79</v>
+      </c>
+      <c r="H156" t="s">
+        <v>74</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156">
+        <v>3</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>3</v>
+      </c>
+      <c r="N156">
+        <v>5</v>
+      </c>
+      <c r="O156" t="s">
+        <v>190</v>
+      </c>
+      <c r="P156" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q156">
+        <v>2.38</v>
+      </c>
+      <c r="R156">
+        <v>2.05</v>
+      </c>
+      <c r="S156">
+        <v>6</v>
+      </c>
+      <c r="T156">
+        <v>1.5</v>
+      </c>
+      <c r="U156">
+        <v>2.5</v>
+      </c>
+      <c r="V156">
+        <v>3.5</v>
+      </c>
+      <c r="W156">
+        <v>1.29</v>
+      </c>
+      <c r="X156">
+        <v>11</v>
+      </c>
+      <c r="Y156">
+        <v>1.05</v>
+      </c>
+      <c r="Z156">
+        <v>1.73</v>
+      </c>
+      <c r="AA156">
+        <v>3.5</v>
+      </c>
+      <c r="AB156">
+        <v>5.25</v>
+      </c>
+      <c r="AC156">
+        <v>1.06</v>
+      </c>
+      <c r="AD156">
+        <v>6.15</v>
+      </c>
+      <c r="AE156">
+        <v>1.42</v>
+      </c>
+      <c r="AF156">
+        <v>2.56</v>
+      </c>
+      <c r="AG156">
+        <v>2.35</v>
+      </c>
+      <c r="AH156">
+        <v>1.56</v>
+      </c>
+      <c r="AI156">
+        <v>2.2</v>
+      </c>
+      <c r="AJ156">
+        <v>1.62</v>
+      </c>
+      <c r="AK156">
+        <v>1.15</v>
+      </c>
+      <c r="AL156">
+        <v>1.3</v>
+      </c>
+      <c r="AM156">
+        <v>2.15</v>
+      </c>
+      <c r="AN156">
+        <v>2.11</v>
+      </c>
+      <c r="AO156">
+        <v>0.75</v>
+      </c>
+      <c r="AP156">
+        <v>1.9</v>
+      </c>
+      <c r="AQ156">
+        <v>1</v>
+      </c>
+      <c r="AR156">
+        <v>1.41</v>
+      </c>
+      <c r="AS156">
+        <v>1.11</v>
+      </c>
+      <c r="AT156">
+        <v>2.52</v>
+      </c>
+      <c r="AU156">
+        <v>3</v>
+      </c>
+      <c r="AV156">
+        <v>4</v>
+      </c>
+      <c r="AW156">
+        <v>13</v>
+      </c>
+      <c r="AX156">
+        <v>7</v>
+      </c>
+      <c r="AY156">
+        <v>20</v>
+      </c>
+      <c r="AZ156">
+        <v>12</v>
+      </c>
+      <c r="BA156">
+        <v>7</v>
+      </c>
+      <c r="BB156">
+        <v>1</v>
+      </c>
+      <c r="BC156">
+        <v>8</v>
+      </c>
+      <c r="BD156">
+        <v>1.46</v>
+      </c>
+      <c r="BE156">
+        <v>6.75</v>
+      </c>
+      <c r="BF156">
+        <v>3.05</v>
+      </c>
+      <c r="BG156">
+        <v>1.45</v>
+      </c>
+      <c r="BH156">
+        <v>2.48</v>
+      </c>
+      <c r="BI156">
+        <v>1.77</v>
+      </c>
+      <c r="BJ156">
+        <v>1.89</v>
+      </c>
+      <c r="BK156">
+        <v>2.23</v>
+      </c>
+      <c r="BL156">
+        <v>1.55</v>
+      </c>
+      <c r="BM156">
+        <v>2.9</v>
+      </c>
+      <c r="BN156">
+        <v>1.34</v>
+      </c>
+      <c r="BO156">
+        <v>3.9</v>
+      </c>
+      <c r="BP156">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7574716</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45675.625</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>81</v>
+      </c>
+      <c r="H157" t="s">
+        <v>70</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>2</v>
+      </c>
+      <c r="K157">
+        <v>2</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>3</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>90</v>
+      </c>
+      <c r="P157" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q157">
+        <v>8.5</v>
+      </c>
+      <c r="R157">
+        <v>2.75</v>
+      </c>
+      <c r="S157">
+        <v>1.67</v>
+      </c>
+      <c r="T157">
+        <v>1.25</v>
+      </c>
+      <c r="U157">
+        <v>3.75</v>
+      </c>
+      <c r="V157">
+        <v>2.2</v>
+      </c>
+      <c r="W157">
+        <v>1.62</v>
+      </c>
+      <c r="X157">
+        <v>5</v>
+      </c>
+      <c r="Y157">
+        <v>1.17</v>
+      </c>
+      <c r="Z157">
+        <v>9</v>
+      </c>
+      <c r="AA157">
+        <v>5.75</v>
+      </c>
+      <c r="AB157">
+        <v>1.3</v>
+      </c>
+      <c r="AC157">
+        <v>1.01</v>
+      </c>
+      <c r="AD157">
+        <v>17</v>
+      </c>
+      <c r="AE157">
+        <v>1.1</v>
+      </c>
+      <c r="AF157">
+        <v>5.1</v>
+      </c>
+      <c r="AG157">
+        <v>1.47</v>
+      </c>
+      <c r="AH157">
+        <v>2.5</v>
+      </c>
+      <c r="AI157">
+        <v>1.95</v>
+      </c>
+      <c r="AJ157">
+        <v>1.8</v>
+      </c>
+      <c r="AK157">
+        <v>4.05</v>
+      </c>
+      <c r="AL157">
+        <v>1.12</v>
+      </c>
+      <c r="AM157">
+        <v>1.04</v>
+      </c>
+      <c r="AN157">
+        <v>2</v>
+      </c>
+      <c r="AO157">
+        <v>2.22</v>
+      </c>
+      <c r="AP157">
+        <v>1.78</v>
+      </c>
+      <c r="AQ157">
+        <v>2.3</v>
+      </c>
+      <c r="AR157">
+        <v>1.39</v>
+      </c>
+      <c r="AS157">
+        <v>1.92</v>
+      </c>
+      <c r="AT157">
+        <v>3.31</v>
+      </c>
+      <c r="AU157">
+        <v>2</v>
+      </c>
+      <c r="AV157">
+        <v>12</v>
+      </c>
+      <c r="AW157">
+        <v>1</v>
+      </c>
+      <c r="AX157">
+        <v>17</v>
+      </c>
+      <c r="AY157">
+        <v>4</v>
+      </c>
+      <c r="AZ157">
+        <v>32</v>
+      </c>
+      <c r="BA157">
+        <v>0</v>
+      </c>
+      <c r="BB157">
+        <v>8</v>
+      </c>
+      <c r="BC157">
+        <v>8</v>
+      </c>
+      <c r="BD157">
+        <v>5.8</v>
+      </c>
+      <c r="BE157">
+        <v>9.5</v>
+      </c>
+      <c r="BF157">
+        <v>1.15</v>
+      </c>
+      <c r="BG157">
+        <v>1.18</v>
+      </c>
+      <c r="BH157">
+        <v>4.1</v>
+      </c>
+      <c r="BI157">
+        <v>1.34</v>
+      </c>
+      <c r="BJ157">
+        <v>2.9</v>
+      </c>
+      <c r="BK157">
+        <v>1.54</v>
+      </c>
+      <c r="BL157">
+        <v>2.25</v>
+      </c>
+      <c r="BM157">
+        <v>1.83</v>
+      </c>
+      <c r="BN157">
+        <v>1.83</v>
+      </c>
+      <c r="BO157">
+        <v>2.25</v>
+      </c>
+      <c r="BP157">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7574723</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45675.72916666666</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>85</v>
+      </c>
+      <c r="H158" t="s">
+        <v>78</v>
+      </c>
+      <c r="I158">
+        <v>2</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>2</v>
+      </c>
+      <c r="L158">
+        <v>2</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>4</v>
+      </c>
+      <c r="O158" t="s">
+        <v>191</v>
+      </c>
+      <c r="P158" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q158">
+        <v>2.2</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>6</v>
+      </c>
+      <c r="T158">
+        <v>1.4</v>
+      </c>
+      <c r="U158">
+        <v>2.75</v>
+      </c>
+      <c r="V158">
+        <v>3</v>
+      </c>
+      <c r="W158">
+        <v>1.36</v>
+      </c>
+      <c r="X158">
+        <v>8</v>
+      </c>
+      <c r="Y158">
+        <v>1.08</v>
+      </c>
+      <c r="Z158">
+        <v>1.57</v>
+      </c>
+      <c r="AA158">
+        <v>4</v>
+      </c>
+      <c r="AB158">
+        <v>6</v>
+      </c>
+      <c r="AC158">
+        <v>1.05</v>
+      </c>
+      <c r="AD158">
+        <v>11</v>
+      </c>
+      <c r="AE158">
+        <v>1.3</v>
+      </c>
+      <c r="AF158">
+        <v>3.4</v>
+      </c>
+      <c r="AG158">
+        <v>1.93</v>
+      </c>
+      <c r="AH158">
+        <v>1.81</v>
+      </c>
+      <c r="AI158">
+        <v>1.95</v>
+      </c>
+      <c r="AJ158">
+        <v>1.8</v>
+      </c>
+      <c r="AK158">
+        <v>1.14</v>
+      </c>
+      <c r="AL158">
+        <v>1.2</v>
+      </c>
+      <c r="AM158">
+        <v>2.35</v>
+      </c>
+      <c r="AN158">
+        <v>1.88</v>
+      </c>
+      <c r="AO158">
+        <v>0.78</v>
+      </c>
+      <c r="AP158">
+        <v>1.78</v>
+      </c>
+      <c r="AQ158">
+        <v>0.8</v>
+      </c>
+      <c r="AR158">
+        <v>1.33</v>
+      </c>
+      <c r="AS158">
+        <v>1.11</v>
+      </c>
+      <c r="AT158">
+        <v>2.44</v>
+      </c>
+      <c r="AU158">
+        <v>8</v>
+      </c>
+      <c r="AV158">
+        <v>6</v>
+      </c>
+      <c r="AW158">
+        <v>8</v>
+      </c>
+      <c r="AX158">
+        <v>14</v>
+      </c>
+      <c r="AY158">
+        <v>20</v>
+      </c>
+      <c r="AZ158">
+        <v>22</v>
+      </c>
+      <c r="BA158">
+        <v>9</v>
+      </c>
+      <c r="BB158">
+        <v>5</v>
+      </c>
+      <c r="BC158">
+        <v>14</v>
+      </c>
+      <c r="BD158">
+        <v>1.38</v>
+      </c>
+      <c r="BE158">
+        <v>7.5</v>
+      </c>
+      <c r="BF158">
+        <v>3.3</v>
+      </c>
+      <c r="BG158">
+        <v>1.19</v>
+      </c>
+      <c r="BH158">
+        <v>3.95</v>
+      </c>
+      <c r="BI158">
+        <v>1.34</v>
+      </c>
+      <c r="BJ158">
+        <v>2.85</v>
+      </c>
+      <c r="BK158">
+        <v>1.58</v>
+      </c>
+      <c r="BL158">
+        <v>2.18</v>
+      </c>
+      <c r="BM158">
+        <v>1.9</v>
+      </c>
+      <c r="BN158">
+        <v>1.76</v>
+      </c>
+      <c r="BO158">
+        <v>2.38</v>
+      </c>
+      <c r="BP158">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,12 @@
     <t>['20', '40']</t>
   </si>
   <si>
+    <t>['20', '34', '45+6']</t>
+  </si>
+  <si>
+    <t>['11', '53', '90+4']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -824,6 +830,15 @@
   </si>
   <si>
     <t>['56', '72']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['48']</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1647,7 +1662,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2265,7 +2280,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2677,7 +2692,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3295,7 +3310,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3376,7 +3391,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ11">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3501,7 +3516,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3579,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3788,7 +3803,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ13">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3913,7 +3928,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -3991,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ14">
         <v>2.3</v>
@@ -4325,7 +4340,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4403,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -4737,7 +4752,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4818,7 +4833,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ18">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4943,7 +4958,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5021,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19">
         <v>1.11</v>
@@ -5149,7 +5164,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5355,7 +5370,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7003,7 +7018,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7081,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ29">
         <v>1.75</v>
@@ -7209,7 +7224,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7290,7 +7305,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ30">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR30">
         <v>0.55</v>
@@ -7415,7 +7430,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7493,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
         <v>1.38</v>
@@ -7908,7 +7923,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ33">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR33">
         <v>2.25</v>
@@ -8111,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ34">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR34">
         <v>1.18</v>
@@ -8445,7 +8460,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8729,10 +8744,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ37">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR37">
         <v>1.77</v>
@@ -8857,7 +8872,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9063,7 +9078,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9475,7 +9490,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9681,7 +9696,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9887,7 +9902,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -9968,7 +9983,7 @@
         <v>3</v>
       </c>
       <c r="AQ43">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR43">
         <v>2.13</v>
@@ -10299,7 +10314,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10505,7 +10520,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10583,7 +10598,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10711,7 +10726,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10789,10 +10804,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ47">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR47">
         <v>1.27</v>
@@ -10917,7 +10932,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11329,7 +11344,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11410,7 +11425,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ50">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -11613,7 +11628,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ51">
         <v>1.11</v>
@@ -11741,7 +11756,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11819,7 +11834,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ52">
         <v>1.38</v>
@@ -11947,7 +11962,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12234,7 +12249,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ54">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR54">
         <v>1.92</v>
@@ -12359,7 +12374,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12565,7 +12580,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12771,7 +12786,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>3.6</v>
@@ -12849,7 +12864,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ57">
         <v>0.78</v>
@@ -12977,7 +12992,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13183,7 +13198,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -14294,7 +14309,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ64">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.27</v>
@@ -14703,7 +14718,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ66">
         <v>0.25</v>
@@ -14909,7 +14924,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ67">
         <v>1.5</v>
@@ -15118,7 +15133,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR68">
         <v>0.83</v>
@@ -15655,7 +15670,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15861,7 +15876,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -15942,7 +15957,7 @@
         <v>3</v>
       </c>
       <c r="AQ72">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR72">
         <v>2.36</v>
@@ -16273,7 +16288,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16479,7 +16494,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16685,7 +16700,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16891,7 +16906,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17178,7 +17193,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR78">
         <v>1.68</v>
@@ -17509,7 +17524,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17587,7 +17602,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ80">
         <v>1.11</v>
@@ -17715,7 +17730,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17796,7 +17811,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR81">
         <v>1.3</v>
@@ -17921,7 +17936,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18127,7 +18142,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18333,7 +18348,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18539,7 +18554,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18617,7 +18632,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -18745,7 +18760,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19157,7 +19172,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19238,7 +19253,7 @@
         <v>1</v>
       </c>
       <c r="AQ88">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR88">
         <v>0.89</v>
@@ -19647,7 +19662,7 @@
         <v>1.5</v>
       </c>
       <c r="AP90">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19775,7 +19790,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19853,7 +19868,7 @@
         <v>0.4</v>
       </c>
       <c r="AP91">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ91">
         <v>0.67</v>
@@ -19981,7 +19996,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20062,7 +20077,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ92">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR92">
         <v>1.25</v>
@@ -20268,7 +20283,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ93">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR93">
         <v>0.99</v>
@@ -20599,7 +20614,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20883,7 +20898,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ96">
         <v>0.33</v>
@@ -21217,7 +21232,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21504,7 +21519,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ99">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR99">
         <v>2.36</v>
@@ -21835,7 +21850,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22119,7 +22134,7 @@
         <v>1.33</v>
       </c>
       <c r="AP102">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22247,7 +22262,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22453,7 +22468,7 @@
         <v>154</v>
       </c>
       <c r="P104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22659,7 +22674,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22865,7 +22880,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -22946,7 +22961,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ106">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR106">
         <v>1.19</v>
@@ -23561,7 +23576,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ109">
         <v>2.3</v>
@@ -23689,7 +23704,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23895,7 +23910,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -23973,7 +23988,7 @@
         <v>0.33</v>
       </c>
       <c r="AP111">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ111">
         <v>0.33</v>
@@ -24594,7 +24609,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ114">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR114">
         <v>1.09</v>
@@ -24800,7 +24815,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ115">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25006,7 +25021,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ116">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR116">
         <v>1.23</v>
@@ -25131,7 +25146,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25209,7 +25224,7 @@
         <v>0.67</v>
       </c>
       <c r="AP117">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117">
         <v>0.8</v>
@@ -25337,7 +25352,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q118">
         <v>3.5</v>
@@ -25621,7 +25636,7 @@
         <v>0.86</v>
       </c>
       <c r="AP119">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ119">
         <v>0.78</v>
@@ -25749,7 +25764,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26161,7 +26176,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26367,7 +26382,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26573,7 +26588,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -26985,7 +27000,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27191,7 +27206,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27269,7 +27284,7 @@
         <v>1.83</v>
       </c>
       <c r="AP127">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ127">
         <v>1.75</v>
@@ -27397,7 +27412,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27603,7 +27618,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27684,7 +27699,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ129">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR129">
         <v>1.02</v>
@@ -27890,7 +27905,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ130">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28015,7 +28030,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28093,10 +28108,10 @@
         <v>1.67</v>
       </c>
       <c r="AP131">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ131">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28221,7 +28236,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28302,7 +28317,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ132">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR132">
         <v>1.35</v>
@@ -28505,7 +28520,7 @@
         <v>2.57</v>
       </c>
       <c r="AP133">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ133">
         <v>2.3</v>
@@ -28633,7 +28648,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29123,7 +29138,7 @@
         <v>0.43</v>
       </c>
       <c r="AP136">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ136">
         <v>0.44</v>
@@ -29457,7 +29472,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29663,7 +29678,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30075,7 +30090,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30281,7 +30296,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30487,7 +30502,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30899,7 +30914,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31105,7 +31120,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31311,7 +31326,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31389,10 +31404,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ147">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR147">
         <v>1.11</v>
@@ -31517,7 +31532,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31598,7 +31613,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ148">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR148">
         <v>2.01</v>
@@ -31723,7 +31738,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32010,7 +32025,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ150">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR150">
         <v>1.34</v>
@@ -32135,7 +32150,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32341,7 +32356,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32419,7 +32434,7 @@
         <v>0.43</v>
       </c>
       <c r="AP152">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32547,7 +32562,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32625,7 +32640,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ153">
         <v>0.44</v>
@@ -32831,10 +32846,10 @@
         <v>1.86</v>
       </c>
       <c r="AP154">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ154">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR154">
         <v>1.23</v>
@@ -33165,7 +33180,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33371,7 +33386,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33577,7 +33592,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33734,6 +33749,830 @@
       </c>
       <c r="BP158">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7574724</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45676.52083333334</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>82</v>
+      </c>
+      <c r="H159" t="s">
+        <v>71</v>
+      </c>
+      <c r="I159">
+        <v>3</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>4</v>
+      </c>
+      <c r="L159">
+        <v>3</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>4</v>
+      </c>
+      <c r="O159" t="s">
+        <v>192</v>
+      </c>
+      <c r="P159" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q159">
+        <v>2.88</v>
+      </c>
+      <c r="R159">
+        <v>2</v>
+      </c>
+      <c r="S159">
+        <v>4.33</v>
+      </c>
+      <c r="T159">
+        <v>1.5</v>
+      </c>
+      <c r="U159">
+        <v>2.5</v>
+      </c>
+      <c r="V159">
+        <v>3.4</v>
+      </c>
+      <c r="W159">
+        <v>1.3</v>
+      </c>
+      <c r="X159">
+        <v>10</v>
+      </c>
+      <c r="Y159">
+        <v>1.06</v>
+      </c>
+      <c r="Z159">
+        <v>2.1</v>
+      </c>
+      <c r="AA159">
+        <v>3.1</v>
+      </c>
+      <c r="AB159">
+        <v>3.5</v>
+      </c>
+      <c r="AC159">
+        <v>1.08</v>
+      </c>
+      <c r="AD159">
+        <v>8.5</v>
+      </c>
+      <c r="AE159">
+        <v>1.42</v>
+      </c>
+      <c r="AF159">
+        <v>2.85</v>
+      </c>
+      <c r="AG159">
+        <v>2.25</v>
+      </c>
+      <c r="AH159">
+        <v>1.57</v>
+      </c>
+      <c r="AI159">
+        <v>1.95</v>
+      </c>
+      <c r="AJ159">
+        <v>1.8</v>
+      </c>
+      <c r="AK159">
+        <v>1.28</v>
+      </c>
+      <c r="AL159">
+        <v>1.28</v>
+      </c>
+      <c r="AM159">
+        <v>1.78</v>
+      </c>
+      <c r="AN159">
+        <v>1.63</v>
+      </c>
+      <c r="AO159">
+        <v>0.63</v>
+      </c>
+      <c r="AP159">
+        <v>1.78</v>
+      </c>
+      <c r="AQ159">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR159">
+        <v>1.19</v>
+      </c>
+      <c r="AS159">
+        <v>1</v>
+      </c>
+      <c r="AT159">
+        <v>2.19</v>
+      </c>
+      <c r="AU159">
+        <v>8</v>
+      </c>
+      <c r="AV159">
+        <v>5</v>
+      </c>
+      <c r="AW159">
+        <v>9</v>
+      </c>
+      <c r="AX159">
+        <v>12</v>
+      </c>
+      <c r="AY159">
+        <v>17</v>
+      </c>
+      <c r="AZ159">
+        <v>17</v>
+      </c>
+      <c r="BA159">
+        <v>4</v>
+      </c>
+      <c r="BB159">
+        <v>6</v>
+      </c>
+      <c r="BC159">
+        <v>10</v>
+      </c>
+      <c r="BD159">
+        <v>1.74</v>
+      </c>
+      <c r="BE159">
+        <v>6.75</v>
+      </c>
+      <c r="BF159">
+        <v>2.3</v>
+      </c>
+      <c r="BG159">
+        <v>1.26</v>
+      </c>
+      <c r="BH159">
+        <v>3.35</v>
+      </c>
+      <c r="BI159">
+        <v>1.46</v>
+      </c>
+      <c r="BJ159">
+        <v>2.45</v>
+      </c>
+      <c r="BK159">
+        <v>1.75</v>
+      </c>
+      <c r="BL159">
+        <v>1.92</v>
+      </c>
+      <c r="BM159">
+        <v>2.18</v>
+      </c>
+      <c r="BN159">
+        <v>1.58</v>
+      </c>
+      <c r="BO159">
+        <v>2.8</v>
+      </c>
+      <c r="BP159">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7574722</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45676.52083333334</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160" t="s">
+        <v>76</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160" t="s">
+        <v>90</v>
+      </c>
+      <c r="P160" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q160">
+        <v>2.63</v>
+      </c>
+      <c r="R160">
+        <v>1.95</v>
+      </c>
+      <c r="S160">
+        <v>5</v>
+      </c>
+      <c r="T160">
+        <v>1.57</v>
+      </c>
+      <c r="U160">
+        <v>2.25</v>
+      </c>
+      <c r="V160">
+        <v>3.75</v>
+      </c>
+      <c r="W160">
+        <v>1.25</v>
+      </c>
+      <c r="X160">
+        <v>11</v>
+      </c>
+      <c r="Y160">
+        <v>1.05</v>
+      </c>
+      <c r="Z160">
+        <v>1.85</v>
+      </c>
+      <c r="AA160">
+        <v>3.2</v>
+      </c>
+      <c r="AB160">
+        <v>4.4</v>
+      </c>
+      <c r="AC160">
+        <v>1.1</v>
+      </c>
+      <c r="AD160">
+        <v>7.5</v>
+      </c>
+      <c r="AE160">
+        <v>1.5</v>
+      </c>
+      <c r="AF160">
+        <v>2.4</v>
+      </c>
+      <c r="AG160">
+        <v>2.37</v>
+      </c>
+      <c r="AH160">
+        <v>1.53</v>
+      </c>
+      <c r="AI160">
+        <v>2.2</v>
+      </c>
+      <c r="AJ160">
+        <v>1.62</v>
+      </c>
+      <c r="AK160">
+        <v>1.2</v>
+      </c>
+      <c r="AL160">
+        <v>1.28</v>
+      </c>
+      <c r="AM160">
+        <v>1.9</v>
+      </c>
+      <c r="AN160">
+        <v>1.88</v>
+      </c>
+      <c r="AO160">
+        <v>0.78</v>
+      </c>
+      <c r="AP160">
+        <v>1.78</v>
+      </c>
+      <c r="AQ160">
+        <v>0.8</v>
+      </c>
+      <c r="AR160">
+        <v>1.14</v>
+      </c>
+      <c r="AS160">
+        <v>1.01</v>
+      </c>
+      <c r="AT160">
+        <v>2.15</v>
+      </c>
+      <c r="AU160">
+        <v>2</v>
+      </c>
+      <c r="AV160">
+        <v>2</v>
+      </c>
+      <c r="AW160">
+        <v>14</v>
+      </c>
+      <c r="AX160">
+        <v>5</v>
+      </c>
+      <c r="AY160">
+        <v>16</v>
+      </c>
+      <c r="AZ160">
+        <v>7</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>3</v>
+      </c>
+      <c r="BC160">
+        <v>9</v>
+      </c>
+      <c r="BD160">
+        <v>1.5</v>
+      </c>
+      <c r="BE160">
+        <v>6.75</v>
+      </c>
+      <c r="BF160">
+        <v>2.8</v>
+      </c>
+      <c r="BG160">
+        <v>1.27</v>
+      </c>
+      <c r="BH160">
+        <v>3.3</v>
+      </c>
+      <c r="BI160">
+        <v>1.48</v>
+      </c>
+      <c r="BJ160">
+        <v>2.4</v>
+      </c>
+      <c r="BK160">
+        <v>1.77</v>
+      </c>
+      <c r="BL160">
+        <v>1.9</v>
+      </c>
+      <c r="BM160">
+        <v>2.2</v>
+      </c>
+      <c r="BN160">
+        <v>1.57</v>
+      </c>
+      <c r="BO160">
+        <v>2.8</v>
+      </c>
+      <c r="BP160">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7574721</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45676.625</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>87</v>
+      </c>
+      <c r="H161" t="s">
+        <v>77</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161" t="s">
+        <v>90</v>
+      </c>
+      <c r="P161" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q161">
+        <v>5</v>
+      </c>
+      <c r="R161">
+        <v>2.25</v>
+      </c>
+      <c r="S161">
+        <v>2.25</v>
+      </c>
+      <c r="T161">
+        <v>1.36</v>
+      </c>
+      <c r="U161">
+        <v>3</v>
+      </c>
+      <c r="V161">
+        <v>2.63</v>
+      </c>
+      <c r="W161">
+        <v>1.44</v>
+      </c>
+      <c r="X161">
+        <v>7</v>
+      </c>
+      <c r="Y161">
+        <v>1.1</v>
+      </c>
+      <c r="Z161">
+        <v>4.7</v>
+      </c>
+      <c r="AA161">
+        <v>3.85</v>
+      </c>
+      <c r="AB161">
+        <v>1.68</v>
+      </c>
+      <c r="AC161">
+        <v>1.03</v>
+      </c>
+      <c r="AD161">
+        <v>13</v>
+      </c>
+      <c r="AE161">
+        <v>1.25</v>
+      </c>
+      <c r="AF161">
+        <v>3.75</v>
+      </c>
+      <c r="AG161">
+        <v>1.8</v>
+      </c>
+      <c r="AH161">
+        <v>2</v>
+      </c>
+      <c r="AI161">
+        <v>1.8</v>
+      </c>
+      <c r="AJ161">
+        <v>1.95</v>
+      </c>
+      <c r="AK161">
+        <v>2.15</v>
+      </c>
+      <c r="AL161">
+        <v>1.2</v>
+      </c>
+      <c r="AM161">
+        <v>1.18</v>
+      </c>
+      <c r="AN161">
+        <v>1.56</v>
+      </c>
+      <c r="AO161">
+        <v>2.38</v>
+      </c>
+      <c r="AP161">
+        <v>1.4</v>
+      </c>
+      <c r="AQ161">
+        <v>2.44</v>
+      </c>
+      <c r="AR161">
+        <v>1.17</v>
+      </c>
+      <c r="AS161">
+        <v>1.42</v>
+      </c>
+      <c r="AT161">
+        <v>2.59</v>
+      </c>
+      <c r="AU161">
+        <v>6</v>
+      </c>
+      <c r="AV161">
+        <v>6</v>
+      </c>
+      <c r="AW161">
+        <v>4</v>
+      </c>
+      <c r="AX161">
+        <v>10</v>
+      </c>
+      <c r="AY161">
+        <v>13</v>
+      </c>
+      <c r="AZ161">
+        <v>18</v>
+      </c>
+      <c r="BA161">
+        <v>1</v>
+      </c>
+      <c r="BB161">
+        <v>8</v>
+      </c>
+      <c r="BC161">
+        <v>9</v>
+      </c>
+      <c r="BD161">
+        <v>2.65</v>
+      </c>
+      <c r="BE161">
+        <v>6.75</v>
+      </c>
+      <c r="BF161">
+        <v>1.58</v>
+      </c>
+      <c r="BG161">
+        <v>1.25</v>
+      </c>
+      <c r="BH161">
+        <v>3.45</v>
+      </c>
+      <c r="BI161">
+        <v>1.42</v>
+      </c>
+      <c r="BJ161">
+        <v>2.55</v>
+      </c>
+      <c r="BK161">
+        <v>1.7</v>
+      </c>
+      <c r="BL161">
+        <v>2</v>
+      </c>
+      <c r="BM161">
+        <v>2.08</v>
+      </c>
+      <c r="BN161">
+        <v>1.63</v>
+      </c>
+      <c r="BO161">
+        <v>2.65</v>
+      </c>
+      <c r="BP161">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7574717</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45676.72916666666</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>80</v>
+      </c>
+      <c r="H162" t="s">
+        <v>73</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>3</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>4</v>
+      </c>
+      <c r="O162" t="s">
+        <v>193</v>
+      </c>
+      <c r="P162" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q162">
+        <v>8</v>
+      </c>
+      <c r="R162">
+        <v>2.25</v>
+      </c>
+      <c r="S162">
+        <v>1.95</v>
+      </c>
+      <c r="T162">
+        <v>1.4</v>
+      </c>
+      <c r="U162">
+        <v>2.75</v>
+      </c>
+      <c r="V162">
+        <v>3</v>
+      </c>
+      <c r="W162">
+        <v>1.36</v>
+      </c>
+      <c r="X162">
+        <v>8</v>
+      </c>
+      <c r="Y162">
+        <v>1.08</v>
+      </c>
+      <c r="Z162">
+        <v>7.5</v>
+      </c>
+      <c r="AA162">
+        <v>4.4</v>
+      </c>
+      <c r="AB162">
+        <v>1.4</v>
+      </c>
+      <c r="AC162">
+        <v>1.04</v>
+      </c>
+      <c r="AD162">
+        <v>11</v>
+      </c>
+      <c r="AE162">
+        <v>1.3</v>
+      </c>
+      <c r="AF162">
+        <v>3.4</v>
+      </c>
+      <c r="AG162">
+        <v>1.91</v>
+      </c>
+      <c r="AH162">
+        <v>1.83</v>
+      </c>
+      <c r="AI162">
+        <v>2.25</v>
+      </c>
+      <c r="AJ162">
+        <v>1.57</v>
+      </c>
+      <c r="AK162">
+        <v>2.95</v>
+      </c>
+      <c r="AL162">
+        <v>1.16</v>
+      </c>
+      <c r="AM162">
+        <v>1.07</v>
+      </c>
+      <c r="AN162">
+        <v>1.63</v>
+      </c>
+      <c r="AO162">
+        <v>1.63</v>
+      </c>
+      <c r="AP162">
+        <v>1.78</v>
+      </c>
+      <c r="AQ162">
+        <v>1.44</v>
+      </c>
+      <c r="AR162">
+        <v>1.23</v>
+      </c>
+      <c r="AS162">
+        <v>1.28</v>
+      </c>
+      <c r="AT162">
+        <v>2.51</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>4</v>
+      </c>
+      <c r="AW162">
+        <v>4</v>
+      </c>
+      <c r="AX162">
+        <v>11</v>
+      </c>
+      <c r="AY162">
+        <v>9</v>
+      </c>
+      <c r="AZ162">
+        <v>19</v>
+      </c>
+      <c r="BA162">
+        <v>4</v>
+      </c>
+      <c r="BB162">
+        <v>6</v>
+      </c>
+      <c r="BC162">
+        <v>10</v>
+      </c>
+      <c r="BD162">
+        <v>4.1</v>
+      </c>
+      <c r="BE162">
+        <v>8</v>
+      </c>
+      <c r="BF162">
+        <v>1.27</v>
+      </c>
+      <c r="BG162">
+        <v>1.36</v>
+      </c>
+      <c r="BH162">
+        <v>2.8</v>
+      </c>
+      <c r="BI162">
+        <v>1.6</v>
+      </c>
+      <c r="BJ162">
+        <v>2.14</v>
+      </c>
+      <c r="BK162">
+        <v>1.97</v>
+      </c>
+      <c r="BL162">
+        <v>1.71</v>
+      </c>
+      <c r="BM162">
+        <v>2.5</v>
+      </c>
+      <c r="BN162">
+        <v>1.44</v>
+      </c>
+      <c r="BO162">
+        <v>3.3</v>
+      </c>
+      <c r="BP162">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -598,6 +598,9 @@
     <t>['11', '53', '90+4']</t>
   </si>
   <si>
+    <t>['45', '90+3']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -839,6 +842,9 @@
   </si>
   <si>
     <t>['48']</t>
+  </si>
+  <si>
+    <t>['30', '43', '50']</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1662,7 +1668,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2280,7 +2286,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2692,7 +2698,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q8">
         <v>3.5</v>
@@ -3310,7 +3316,7 @@
         <v>90</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>6.5</v>
@@ -3516,7 +3522,7 @@
         <v>96</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>3</v>
@@ -3928,7 +3934,7 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -4215,7 +4221,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ15">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4340,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -4752,7 +4758,7 @@
         <v>90</v>
       </c>
       <c r="P18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q18">
         <v>5.5</v>
@@ -4830,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ18">
         <v>2.44</v>
@@ -4958,7 +4964,7 @@
         <v>90</v>
       </c>
       <c r="P19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q19">
         <v>3.1</v>
@@ -5164,7 +5170,7 @@
         <v>90</v>
       </c>
       <c r="P20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q20">
         <v>9.6</v>
@@ -5370,7 +5376,7 @@
         <v>90</v>
       </c>
       <c r="P21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q21">
         <v>3.2</v>
@@ -7018,7 +7024,7 @@
         <v>106</v>
       </c>
       <c r="P29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7224,7 +7230,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7430,7 +7436,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
@@ -7511,7 +7517,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -7714,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8460,7 +8466,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q36">
         <v>2.55</v>
@@ -8872,7 +8878,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q38">
         <v>8.5</v>
@@ -9078,7 +9084,7 @@
         <v>112</v>
       </c>
       <c r="P39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -9490,7 +9496,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -9696,7 +9702,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>1.67</v>
@@ -9902,7 +9908,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q43">
         <v>1.5</v>
@@ -10314,7 +10320,7 @@
         <v>90</v>
       </c>
       <c r="P45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q45">
         <v>2.63</v>
@@ -10520,7 +10526,7 @@
         <v>117</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10726,7 +10732,7 @@
         <v>90</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10932,7 +10938,7 @@
         <v>118</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q48">
         <v>2.65</v>
@@ -11344,7 +11350,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q50">
         <v>4.5</v>
@@ -11756,7 +11762,7 @@
         <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -11837,7 +11843,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ52">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR52">
         <v>1.51</v>
@@ -11962,7 +11968,7 @@
         <v>90</v>
       </c>
       <c r="P53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12374,7 +12380,7 @@
         <v>90</v>
       </c>
       <c r="P55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q55">
         <v>9.5</v>
@@ -12452,7 +12458,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ55">
         <v>1.75</v>
@@ -12580,7 +12586,7 @@
         <v>90</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q56">
         <v>10</v>
@@ -12786,7 +12792,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>3.6</v>
@@ -12992,7 +12998,7 @@
         <v>122</v>
       </c>
       <c r="P58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13198,7 +13204,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59">
         <v>1.57</v>
@@ -15339,7 +15345,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR69">
         <v>2.1</v>
@@ -15670,7 +15676,7 @@
         <v>132</v>
       </c>
       <c r="P71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q71">
         <v>2</v>
@@ -15876,7 +15882,7 @@
         <v>133</v>
       </c>
       <c r="P72" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16288,7 +16294,7 @@
         <v>134</v>
       </c>
       <c r="P74" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q74">
         <v>2.88</v>
@@ -16494,7 +16500,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>3.75</v>
@@ -16700,7 +16706,7 @@
         <v>90</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>4</v>
@@ -16778,7 +16784,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ76">
         <v>0.78</v>
@@ -16906,7 +16912,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q77">
         <v>8</v>
@@ -17524,7 +17530,7 @@
         <v>138</v>
       </c>
       <c r="P80" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q80">
         <v>5</v>
@@ -17730,7 +17736,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81">
         <v>8.5</v>
@@ -17936,7 +17942,7 @@
         <v>139</v>
       </c>
       <c r="P82" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q82">
         <v>1.33</v>
@@ -18142,7 +18148,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18223,7 +18229,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ83">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18348,7 +18354,7 @@
         <v>141</v>
       </c>
       <c r="P84" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q84">
         <v>9</v>
@@ -18554,7 +18560,7 @@
         <v>113</v>
       </c>
       <c r="P85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18760,7 +18766,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q86">
         <v>3.92</v>
@@ -19172,7 +19178,7 @@
         <v>144</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q88">
         <v>4.5</v>
@@ -19790,7 +19796,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q91">
         <v>2.86</v>
@@ -19996,7 +20002,7 @@
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>2.7</v>
@@ -20614,7 +20620,7 @@
         <v>90</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q95">
         <v>3.35</v>
@@ -20692,7 +20698,7 @@
         <v>0</v>
       </c>
       <c r="AP95">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ95">
         <v>0.44</v>
@@ -21232,7 +21238,7 @@
         <v>150</v>
       </c>
       <c r="P98" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21850,7 +21856,7 @@
         <v>153</v>
       </c>
       <c r="P101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>3.6</v>
@@ -22262,7 +22268,7 @@
         <v>90</v>
       </c>
       <c r="P103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>1.57</v>
@@ -22468,7 +22474,7 @@
         <v>154</v>
       </c>
       <c r="P104" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22674,7 +22680,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q105">
         <v>9</v>
@@ -22880,7 +22886,7 @@
         <v>90</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q106">
         <v>5.5</v>
@@ -23373,7 +23379,7 @@
         <v>3</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR108">
         <v>2.03</v>
@@ -23704,7 +23710,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q110">
         <v>1.7</v>
@@ -23910,7 +23916,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24812,7 +24818,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ115">
         <v>0.8</v>
@@ -25146,7 +25152,7 @@
         <v>163</v>
       </c>
       <c r="P117" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q117">
         <v>3.25</v>
@@ -25352,7 +25358,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q118">
         <v>3.5</v>
@@ -25764,7 +25770,7 @@
         <v>165</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q120">
         <v>1.36</v>
@@ -26176,7 +26182,7 @@
         <v>167</v>
       </c>
       <c r="P122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q122">
         <v>11</v>
@@ -26382,7 +26388,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q123">
         <v>3.3</v>
@@ -26463,7 +26469,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ123">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR123">
         <v>1.04</v>
@@ -26588,7 +26594,7 @@
         <v>168</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q124">
         <v>2.05</v>
@@ -27000,7 +27006,7 @@
         <v>170</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27206,7 +27212,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q127">
         <v>8</v>
@@ -27412,7 +27418,7 @@
         <v>171</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>2.9</v>
@@ -27618,7 +27624,7 @@
         <v>149</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q129">
         <v>2.4</v>
@@ -27902,7 +27908,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -28030,7 +28036,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q131">
         <v>7.08</v>
@@ -28236,7 +28242,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q132">
         <v>3.7</v>
@@ -28648,7 +28654,7 @@
         <v>172</v>
       </c>
       <c r="P134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q134">
         <v>2</v>
@@ -29472,7 +29478,7 @@
         <v>174</v>
       </c>
       <c r="P138" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q138">
         <v>3.2</v>
@@ -29678,7 +29684,7 @@
         <v>175</v>
       </c>
       <c r="P139" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q139">
         <v>3.85</v>
@@ -30090,7 +30096,7 @@
         <v>177</v>
       </c>
       <c r="P141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q141">
         <v>4.75</v>
@@ -30296,7 +30302,7 @@
         <v>178</v>
       </c>
       <c r="P142" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q142">
         <v>2.75</v>
@@ -30502,7 +30508,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q143">
         <v>1.85</v>
@@ -30583,7 +30589,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ143">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30914,7 +30920,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q145">
         <v>3.6</v>
@@ -31120,7 +31126,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q146">
         <v>4.75</v>
@@ -31326,7 +31332,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q147">
         <v>2.55</v>
@@ -31532,7 +31538,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q148">
         <v>1.91</v>
@@ -31738,7 +31744,7 @@
         <v>184</v>
       </c>
       <c r="P149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -31816,7 +31822,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ149">
         <v>0.8</v>
@@ -32150,7 +32156,7 @@
         <v>185</v>
       </c>
       <c r="P151" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q151">
         <v>3.25</v>
@@ -32356,7 +32362,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q152">
         <v>3.1</v>
@@ -32562,7 +32568,7 @@
         <v>187</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -33180,7 +33186,7 @@
         <v>190</v>
       </c>
       <c r="P156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q156">
         <v>2.38</v>
@@ -33386,7 +33392,7 @@
         <v>90</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q157">
         <v>8.5</v>
@@ -33592,7 +33598,7 @@
         <v>191</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q158">
         <v>2.2</v>
@@ -33798,7 +33804,7 @@
         <v>192</v>
       </c>
       <c r="P159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q159">
         <v>2.88</v>
@@ -34210,7 +34216,7 @@
         <v>90</v>
       </c>
       <c r="P161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q161">
         <v>5</v>
@@ -34416,7 +34422,7 @@
         <v>193</v>
       </c>
       <c r="P162" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q162">
         <v>8</v>
@@ -34573,6 +34579,212 @@
       </c>
       <c r="BP162">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7574719</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45677.71875</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>86</v>
+      </c>
+      <c r="H163" t="s">
+        <v>72</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>2</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>3</v>
+      </c>
+      <c r="N163">
+        <v>5</v>
+      </c>
+      <c r="O163" t="s">
+        <v>194</v>
+      </c>
+      <c r="P163" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q163">
+        <v>4</v>
+      </c>
+      <c r="R163">
+        <v>1.95</v>
+      </c>
+      <c r="S163">
+        <v>3.1</v>
+      </c>
+      <c r="T163">
+        <v>1.53</v>
+      </c>
+      <c r="U163">
+        <v>2.38</v>
+      </c>
+      <c r="V163">
+        <v>3.5</v>
+      </c>
+      <c r="W163">
+        <v>1.29</v>
+      </c>
+      <c r="X163">
+        <v>11</v>
+      </c>
+      <c r="Y163">
+        <v>1.05</v>
+      </c>
+      <c r="Z163">
+        <v>3.25</v>
+      </c>
+      <c r="AA163">
+        <v>3.1</v>
+      </c>
+      <c r="AB163">
+        <v>2.33</v>
+      </c>
+      <c r="AC163">
+        <v>1.09</v>
+      </c>
+      <c r="AD163">
+        <v>8</v>
+      </c>
+      <c r="AE163">
+        <v>1.45</v>
+      </c>
+      <c r="AF163">
+        <v>2.8</v>
+      </c>
+      <c r="AG163">
+        <v>2.3</v>
+      </c>
+      <c r="AH163">
+        <v>1.55</v>
+      </c>
+      <c r="AI163">
+        <v>2</v>
+      </c>
+      <c r="AJ163">
+        <v>1.75</v>
+      </c>
+      <c r="AK163">
+        <v>1.6</v>
+      </c>
+      <c r="AL163">
+        <v>1.3</v>
+      </c>
+      <c r="AM163">
+        <v>1.36</v>
+      </c>
+      <c r="AN163">
+        <v>0.38</v>
+      </c>
+      <c r="AO163">
+        <v>1.38</v>
+      </c>
+      <c r="AP163">
+        <v>0.33</v>
+      </c>
+      <c r="AQ163">
+        <v>1.56</v>
+      </c>
+      <c r="AR163">
+        <v>1.32</v>
+      </c>
+      <c r="AS163">
+        <v>1.05</v>
+      </c>
+      <c r="AT163">
+        <v>2.37</v>
+      </c>
+      <c r="AU163">
+        <v>6</v>
+      </c>
+      <c r="AV163">
+        <v>8</v>
+      </c>
+      <c r="AW163">
+        <v>5</v>
+      </c>
+      <c r="AX163">
+        <v>3</v>
+      </c>
+      <c r="AY163">
+        <v>12</v>
+      </c>
+      <c r="AZ163">
+        <v>11</v>
+      </c>
+      <c r="BA163">
+        <v>2</v>
+      </c>
+      <c r="BB163">
+        <v>3</v>
+      </c>
+      <c r="BC163">
+        <v>5</v>
+      </c>
+      <c r="BD163">
+        <v>1.96</v>
+      </c>
+      <c r="BE163">
+        <v>6.35</v>
+      </c>
+      <c r="BF163">
+        <v>2.39</v>
+      </c>
+      <c r="BG163">
+        <v>1.33</v>
+      </c>
+      <c r="BH163">
+        <v>2.83</v>
+      </c>
+      <c r="BI163">
+        <v>1.63</v>
+      </c>
+      <c r="BJ163">
+        <v>2.09</v>
+      </c>
+      <c r="BK163">
+        <v>2.11</v>
+      </c>
+      <c r="BL163">
+        <v>1.65</v>
+      </c>
+      <c r="BM163">
+        <v>2.79</v>
+      </c>
+      <c r="BN163">
+        <v>1.36</v>
+      </c>
+      <c r="BO163">
+        <v>3.85</v>
+      </c>
+      <c r="BP163">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Portugal Liga NOS_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1206,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2779,7 +2779,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10">
         <v>1.11</v>
@@ -6278,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25">
         <v>0.33</v>
@@ -6899,7 +6899,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ28">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR28">
         <v>1.72</v>
@@ -8956,7 +8956,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38">
         <v>2.3</v>
@@ -9165,7 +9165,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ39">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR39">
         <v>1.27</v>
@@ -12873,7 +12873,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ57">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR57">
         <v>1.33</v>
@@ -15136,7 +15136,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ68">
         <v>0.5600000000000001</v>
@@ -16787,7 +16787,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ76">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR76">
         <v>1.15</v>
@@ -19053,7 +19053,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ87">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR87">
         <v>1.16</v>
@@ -19256,7 +19256,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ88">
         <v>2.44</v>
@@ -21937,7 +21937,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ101">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22758,7 +22758,7 @@
         <v>1.75</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ105">
         <v>1.75</v>
@@ -25645,7 +25645,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ119">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26054,7 +26054,7 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ121">
         <v>1.5</v>
@@ -29350,7 +29350,7 @@
         <v>0.63</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ137">
         <v>0.67</v>
@@ -29765,7 +29765,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ139">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR139">
         <v>1.09</v>
@@ -34785,6 +34785,212 @@
       </c>
       <c r="BP163">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7574728</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45681.71875</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>78</v>
+      </c>
+      <c r="H164" t="s">
+        <v>84</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>183</v>
+      </c>
+      <c r="P164" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q164">
+        <v>2.85</v>
+      </c>
+      <c r="R164">
+        <v>1.95</v>
+      </c>
+      <c r="S164">
+        <v>3.9</v>
+      </c>
+      <c r="T164">
+        <v>1.49</v>
+      </c>
+      <c r="U164">
+        <v>2.4</v>
+      </c>
+      <c r="V164">
+        <v>3.3</v>
+      </c>
+      <c r="W164">
+        <v>1.29</v>
+      </c>
+      <c r="X164">
+        <v>9.25</v>
+      </c>
+      <c r="Y164">
+        <v>1.05</v>
+      </c>
+      <c r="Z164">
+        <v>2.2</v>
+      </c>
+      <c r="AA164">
+        <v>3.25</v>
+      </c>
+      <c r="AB164">
+        <v>3.3</v>
+      </c>
+      <c r="AC164">
+        <v>1.09</v>
+      </c>
+      <c r="AD164">
+        <v>7</v>
+      </c>
+      <c r="AE164">
+        <v>1.45</v>
+      </c>
+      <c r="AF164">
+        <v>2.7</v>
+      </c>
+      <c r="AG164">
+        <v>2.3</v>
+      </c>
+      <c r="AH164">
+        <v>1.55</v>
+      </c>
+      <c r="AI164">
+        <v>2</v>
+      </c>
+      <c r="AJ164">
+        <v>1.7</v>
+      </c>
+      <c r="AK164">
+        <v>1.31</v>
+      </c>
+      <c r="AL164">
+        <v>1.33</v>
+      </c>
+      <c r="AM164">
+        <v>1.63</v>
+      </c>
+      <c r="AN164">
+        <v>1</v>
+      </c>
+      <c r="AO164">
+        <v>0.78</v>
+      </c>
+      <c r="AP164">
+        <v>1.22</v>
+      </c>
+      <c r="AQ164">
+        <v>0.7</v>
+      </c>
+      <c r="AR164">
+        <v>1.09</v>
+      </c>
+      <c r="AS164">
+        <v>1.19</v>
+      </c>
+      <c r="AT164">
+        <v>2.28</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>11</v>
+      </c>
+      <c r="AX164">
+        <v>6</v>
+      </c>
+      <c r="AY164">
+        <v>23</v>
+      </c>
+      <c r="AZ164">
+        <v>9</v>
+      </c>
+      <c r="BA164">
+        <v>10</v>
+      </c>
+      <c r="BB164">
+        <v>2</v>
+      </c>
+      <c r="BC164">
+        <v>12</v>
+      </c>
+      <c r="BD164">
+        <v>1.55</v>
+      </c>
+      <c r="BE164">
+        <v>6.5</v>
+      </c>
+      <c r="BF164">
+        <v>2.7</v>
+      </c>
+      <c r="BG164">
+        <v>1.3</v>
+      </c>
+      <c r="BH164">
+        <v>3.05</v>
+      </c>
+      <c r="BI164">
+        <v>1.53</v>
+      </c>
+      <c r="BJ164">
+        <v>2.28</v>
+      </c>
+      <c r="BK164">
+        <v>1.86</v>
+      </c>
+      <c r="BL164">
+        <v>1.8</v>
+      </c>
+      <c r="BM164">
+        <v>2.35</v>
+      </c>
+      <c r="BN164">
+        <v>1.5</v>
+      </c>
+      <c r="BO164">
+        <v>3.05</v>
+      </c>
+      <c r="BP164">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
